--- a/data/trans_bre/IP18A03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,93</t>
+          <t>-4,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,34%</t>
+          <t>-5,42%</t>
         </is>
       </c>
     </row>
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,24; -3,91</t>
+          <t>-35,7; -5,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 15,55</t>
+          <t>-14,63; 15,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 19,45</t>
+          <t>-7,39; 21,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 21,04</t>
+          <t>-28,3; 15,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,74; -7,08</t>
+          <t>-50,08; -8,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 25,69</t>
+          <t>-19,68; 26,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 31,61</t>
+          <t>-9,25; 35,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 35,09</t>
+          <t>-31,74; 18,9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,11</t>
+          <t>-7,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,25%</t>
+          <t>-8,31%</t>
         </is>
       </c>
     </row>
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 13,27</t>
+          <t>-6,91; 13,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 5,78</t>
+          <t>-13,73; 7,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 13,03</t>
+          <t>-8,35; 12,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 27,48</t>
+          <t>-30,97; 7,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 20,91</t>
+          <t>-9,71; 22,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 7,93</t>
+          <t>-17,44; 10,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 19,0</t>
+          <t>-10,61; 17,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 69,17</t>
+          <t>-32,19; 8,79</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,71</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-2,94%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 13,4</t>
+          <t>-11,22; 12,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 14,19</t>
+          <t>-13,03; 14,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 4,2</t>
+          <t>-23,21; 3,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 40,51</t>
+          <t>-22,92; 13,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 19,37</t>
+          <t>-14,31; 19,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 30,05</t>
+          <t>-21,85; 30,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 5,73</t>
+          <t>-27,6; 5,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-25,26; 15,57</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,87</t>
+          <t>-9,76</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-24,15%</t>
+          <t>-11,15%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 13,26</t>
+          <t>-13,48; 12,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 12,77</t>
+          <t>-9,49; 12,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 12,26</t>
+          <t>-12,68; 11,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,89; 25,93</t>
+          <t>-39,89; 13,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 23,33</t>
+          <t>-18,65; 21,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 17,27</t>
+          <t>-11,3; 17,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 18,56</t>
+          <t>-16,53; 17,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-42,67; 17,85</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 4,72</t>
+          <t>-35,75; 3,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 27,15</t>
+          <t>-0,25; 27,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 23,66</t>
+          <t>-8,81; 23,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 51,11</t>
+          <t>-36,28; 40,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-53,14; 9,35</t>
+          <t>-53,33; 7,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 40,22</t>
+          <t>-0,19; 41,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 42,98</t>
+          <t>-12,31; 43,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-41,09; 73,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>188,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 20,15</t>
+          <t>-8,57; 20,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 22,88</t>
+          <t>-10,49; 22,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 16,05</t>
+          <t>-14,16; 15,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 40,49</t>
+          <t>-27,89; 19,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 32,23</t>
+          <t>-10,94; 32,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 55,4</t>
+          <t>-18,61; 53,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 26,12</t>
+          <t>-18,49; 25,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,72; 24,9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,82</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>-1,28%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 12,82</t>
+          <t>-6,67; 11,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 6,88</t>
+          <t>-12,94; 7,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 7,01</t>
+          <t>-13,85; 8,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 41,1</t>
+          <t>-20,69; 21,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 20,49</t>
+          <t>-9,59; 19,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 13,63</t>
+          <t>-21,84; 16,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 17,72</t>
+          <t>-26,85; 21,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 316,91</t>
+          <t>-24,81; 31,57</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-4,99</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-6,9%</t>
+          <t>-10,83%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 5,37</t>
+          <t>-13,54; 6,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 3,39</t>
+          <t>-13,28; 3,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 10,44</t>
+          <t>-6,88; 10,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 25,86</t>
+          <t>-34,42; 19,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 11,61</t>
+          <t>-23,55; 12,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 4,95</t>
+          <t>-18,11; 5,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 18,55</t>
+          <t>-10,68; 19,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,1; 103,59</t>
+          <t>-59,33; 52,11</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>-3,01%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 2,73</t>
+          <t>-5,75; 2,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,46</t>
+          <t>-5,22; 3,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,43</t>
+          <t>-3,77; 4,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 16,14</t>
+          <t>-10,84; 6,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 4,34</t>
+          <t>-8,67; 4,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,46</t>
+          <t>-7,63; 5,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 7,0</t>
+          <t>-5,66; 7,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 61,33</t>
+          <t>-13,03; 9,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,7; -5,1</t>
+          <t>-34,78; -5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 15,22</t>
+          <t>-14,34; 15,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 21,23</t>
+          <t>-7,71; 20,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 15,45</t>
+          <t>-30,21; 14,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,08; -8,64</t>
+          <t>-49,15; -9,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 26,29</t>
+          <t>-18,76; 25,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 35,73</t>
+          <t>-10,04; 33,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 18,9</t>
+          <t>-34,1; 18,85</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 13,86</t>
+          <t>-6,76; 14,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 7,2</t>
+          <t>-14,15; 6,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 12,42</t>
+          <t>-7,38; 12,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 7,85</t>
+          <t>-31,63; 7,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 22,4</t>
+          <t>-9,31; 22,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 10,44</t>
+          <t>-18,07; 9,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 17,82</t>
+          <t>-9,53; 18,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 8,79</t>
+          <t>-33,83; 8,18</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 12,88</t>
+          <t>-12,73; 11,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 14,27</t>
+          <t>-13,01; 13,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 3,64</t>
+          <t>-21,73; 4,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 13,3</t>
+          <t>-22,06; 14,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 19,17</t>
+          <t>-15,9; 16,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 30,32</t>
+          <t>-21,4; 30,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 5,24</t>
+          <t>-26,43; 5,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 15,57</t>
+          <t>-24,32; 17,78</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 12,94</t>
+          <t>-14,39; 11,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 12,48</t>
+          <t>-8,62; 12,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 11,18</t>
+          <t>-12,95; 11,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 13,89</t>
+          <t>-37,95; 17,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 21,97</t>
+          <t>-19,92; 20,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 17,67</t>
+          <t>-10,09; 18,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 17,2</t>
+          <t>-16,76; 16,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 17,85</t>
+          <t>-41,82; 22,51</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 3,36</t>
+          <t>-36,16; 3,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 27,16</t>
+          <t>0,96; 27,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 23,15</t>
+          <t>-8,24; 22,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 40,86</t>
+          <t>-37,01; 40,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 7,0</t>
+          <t>-54,53; 6,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 41,83</t>
+          <t>1,3; 41,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 43,02</t>
+          <t>-11,5; 41,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 73,97</t>
+          <t>-44,04; 72,71</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 20,17</t>
+          <t>-9,15; 19,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 22,41</t>
+          <t>-9,92; 22,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 15,63</t>
+          <t>-14,16; 15,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 19,46</t>
+          <t>-24,93; 19,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 32,58</t>
+          <t>-11,8; 32,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 53,89</t>
+          <t>-17,48; 57,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 25,86</t>
+          <t>-18,74; 24,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 24,9</t>
+          <t>-28,46; 25,87</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 11,98</t>
+          <t>-7,32; 12,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 7,78</t>
+          <t>-12,58; 7,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 8,78</t>
+          <t>-13,77; 7,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 21,31</t>
+          <t>-22,32; 18,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 19,52</t>
+          <t>-10,03; 19,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 16,41</t>
+          <t>-21,67; 14,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 21,72</t>
+          <t>-27,04; 18,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 31,57</t>
+          <t>-26,42; 28,49</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 6,17</t>
+          <t>-13,42; 6,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 3,58</t>
+          <t>-13,41; 4,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 10,47</t>
+          <t>-5,82; 10,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 19,55</t>
+          <t>-32,0; 24,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 12,93</t>
+          <t>-23,49; 13,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 5,21</t>
+          <t>-18,22; 6,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 19,16</t>
+          <t>-9,14; 19,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,33; 52,11</t>
+          <t>-55,1; 75,58</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,96</t>
+          <t>-5,9; 3,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,33</t>
+          <t>-4,92; 3,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,62</t>
+          <t>-4,07; 4,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 6,87</t>
+          <t>-11,85; 6,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 4,78</t>
+          <t>-8,89; 4,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 5,26</t>
+          <t>-7,36; 5,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,4</t>
+          <t>-6,18; 7,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 9,06</t>
+          <t>-14,43; 8,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,76</t>
+          <t>-4,91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,42%</t>
+          <t>-5,62%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,78; -5,21</t>
+          <t>-35,24; -3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 15,01</t>
+          <t>-13,96; 15,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 20,39</t>
+          <t>-7,86; 19,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 14,78</t>
+          <t>-29,58; 15,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,15; -9,03</t>
+          <t>-50,74; -7,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 25,23</t>
+          <t>-19,45; 25,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 33,38</t>
+          <t>-10,52; 31,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,1; 18,85</t>
+          <t>-33,13; 19,27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,71</t>
+          <t>-9,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-8,31%</t>
+          <t>-10,08%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 14,03</t>
+          <t>-7,09; 13,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 6,68</t>
+          <t>-15,33; 5,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 12,41</t>
+          <t>-7,95; 13,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 7,31</t>
+          <t>-32,07; 5,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 22,66</t>
+          <t>-9,75; 20,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 9,1</t>
+          <t>-18,91; 7,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 18,67</t>
+          <t>-10,09; 19,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 8,18</t>
+          <t>-34,48; 5,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-3,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,94%</t>
+          <t>-3,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 11,36</t>
+          <t>-12,4; 13,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 13,99</t>
+          <t>-12,1; 14,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 4,0</t>
+          <t>-21,11; 4,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 14,52</t>
+          <t>-23,21; 13,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 16,94</t>
+          <t>-15,5; 19,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 30,54</t>
+          <t>-19,85; 30,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 5,12</t>
+          <t>-25,52; 5,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 17,78</t>
+          <t>-25,27; 17,58</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,76</t>
+          <t>-14,09</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,15%</t>
+          <t>-15,89%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 11,79</t>
+          <t>-13,72; 13,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 12,88</t>
+          <t>-9,28; 12,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 11,13</t>
+          <t>-13,66; 12,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 17,35</t>
+          <t>-42,07; 11,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 20,96</t>
+          <t>-19,12; 23,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 18,0</t>
+          <t>-10,81; 17,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 16,12</t>
+          <t>-17,52; 18,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 22,51</t>
+          <t>-46,09; 13,39</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 3,39</t>
+          <t>-35,68; 4,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 27,49</t>
+          <t>-0,35; 27,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 22,06</t>
+          <t>-8,96; 23,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 40,7</t>
+          <t>-33,65; 34,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,53; 6,27</t>
+          <t>-53,14; 9,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 41,01</t>
+          <t>-0,32; 40,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 41,48</t>
+          <t>-12,34; 42,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 72,71</t>
+          <t>-38,0; 57,82</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 19,9</t>
+          <t>-7,99; 20,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 22,95</t>
+          <t>-8,53; 22,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 15,1</t>
+          <t>-13,89; 16,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 19,21</t>
+          <t>-19,87; 24,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 32,12</t>
+          <t>-9,86; 32,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 57,07</t>
+          <t>-14,98; 55,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 24,67</t>
+          <t>-18,65; 26,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 25,87</t>
+          <t>-23,72; 36,81</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-5,49</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-1,28%</t>
+          <t>-6,91%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 12,34</t>
+          <t>-6,41; 12,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 7,23</t>
+          <t>-13,08; 6,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 7,27</t>
+          <t>-14,75; 7,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 18,91</t>
+          <t>-26,49; 14,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 19,85</t>
+          <t>-8,74; 20,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 14,42</t>
+          <t>-22,22; 13,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 18,76</t>
+          <t>-27,88; 17,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 28,49</t>
+          <t>-31,73; 21,05</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,99</t>
+          <t>-9,21</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-10,83%</t>
+          <t>-19,71%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 6,2</t>
+          <t>-13,71; 5,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 4,69</t>
+          <t>-13,26; 3,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 10,89</t>
+          <t>-6,83; 10,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 24,83</t>
+          <t>-37,18; 21,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 13,14</t>
+          <t>-24,34; 11,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 6,91</t>
+          <t>-18,06; 4,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 19,79</t>
+          <t>-10,52; 18,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-55,1; 75,58</t>
+          <t>-66,69; 62,94</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-3,01%</t>
+          <t>-4,64%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,05</t>
+          <t>-5,96; 2,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,46</t>
+          <t>-4,94; 3,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,64</t>
+          <t>-3,55; 4,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 6,58</t>
+          <t>-13,51; 5,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 4,85</t>
+          <t>-9,02; 4,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 5,39</t>
+          <t>-7,28; 5,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 7,39</t>
+          <t>-5,35; 7,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 8,67</t>
+          <t>-16,1; 6,92</t>
         </is>
       </c>
     </row>
